--- a/files/excel-mastery-1-1.xlsx
+++ b/files/excel-mastery-1-1.xlsx
@@ -541,7 +541,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -549,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -647,9 +650,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,21 +704,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -731,29 +722,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -869,240 +839,283 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1118,10 +1131,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1561,12 +1575,12 @@
   <dimension ref="B2:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="24.08984375" customWidth="1" style="158" min="4" max="4"/>
-    <col width="12.26953125" customWidth="1" style="158" min="5" max="9"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="24.08984375" customWidth="1" min="4" max="4"/>
+    <col width="12.26953125" customWidth="1" min="5" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
+    <row r="2" ht="19.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>1-1. 体裁を統一できる ― 良い例と悪い例の対比</t>
@@ -1574,7 +1588,7 @@
       </c>
       <c r="C2" s="1" t="n"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
+    <row r="5" ht="13.5" customHeight="1">
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="16" t="inlineStr">
         <is>
@@ -1587,7 +1601,7 @@
       <c r="H5" s="17" t="n"/>
       <c r="I5" s="17" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="158">
+    <row r="6" ht="13.5" customHeight="1">
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
@@ -1596,7 +1610,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1" s="158">
+    <row r="7" ht="13.5" customHeight="1">
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>施設</t>
@@ -1628,22 +1642,22 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
+    <row r="8" ht="13.5" customHeight="1">
       <c r="D8" s="10" t="inlineStr">
         <is>
           <t>西伊豆</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="189" t="n">
+      <c r="G8" s="191" t="n">
         <v>0.68</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="44" t="n">
         <v>52000</v>
       </c>
       <c r="I8" s="13">
@@ -1651,22 +1665,22 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
+    <row r="9" ht="13.5" customHeight="1">
       <c r="D9" s="11" t="inlineStr">
         <is>
           <t>熱海</t>
         </is>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="47" t="n">
+      <c r="F9" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="190" t="n">
+      <c r="G9" s="192" t="n">
         <v>0.72</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="46" t="n">
         <v>61000</v>
       </c>
       <c r="I9" s="14">
@@ -1674,22 +1688,22 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
+    <row r="10" ht="13.5" customHeight="1">
       <c r="D10" s="12" t="inlineStr">
         <is>
           <t>箱根</t>
         </is>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="191" t="n">
+      <c r="G10" s="193" t="n">
         <v>0.65</v>
       </c>
-      <c r="H10" s="49" t="n">
+      <c r="H10" s="48" t="n">
         <v>150000</v>
       </c>
       <c r="I10" s="15">
@@ -1697,8 +1711,8 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="122" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
@@ -1715,8 +1729,8 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="122" t="n"/>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="9" t="n"/>
@@ -1751,7 +1765,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="158">
+    <row r="20" ht="13.5" customHeight="1">
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="16" t="inlineStr">
         <is>
@@ -1764,7 +1778,7 @@
       <c r="H20" s="17" t="n"/>
       <c r="I20" s="17" t="n"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="158">
+    <row r="21" ht="13.5" customHeight="1">
       <c r="D21" s="18" t="inlineStr">
         <is>
           <t>施設</t>
@@ -1796,7 +1810,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="158">
+    <row r="22" ht="13.5" customHeight="1">
       <c r="D22" s="18" t="inlineStr">
         <is>
           <t>西伊豆</t>
@@ -1816,12 +1830,12 @@
           <t>52000円</t>
         </is>
       </c>
-      <c r="I22" s="192">
+      <c r="I22" s="194">
         <f>E22*F22*G22*H22/10^3</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="158">
+    <row r="23" ht="13.5" customHeight="1">
       <c r="D23" s="18" t="inlineStr">
         <is>
           <t>熱海</t>
@@ -1844,7 +1858,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="158">
+    <row r="24" ht="13.5" customHeight="1">
       <c r="D24" s="18" t="inlineStr">
         <is>
           <t>箱根</t>
@@ -1867,17 +1881,17 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1" s="158">
-      <c r="D25" s="108" t="inlineStr">
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="D25" s="167" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E25" s="193" t="n"/>
-      <c r="F25" s="193" t="n"/>
-      <c r="G25" s="193" t="n"/>
-      <c r="H25" s="110" t="n"/>
-      <c r="I25" s="43">
+      <c r="E25" s="195" t="n"/>
+      <c r="F25" s="195" t="n"/>
+      <c r="G25" s="195" t="n"/>
+      <c r="H25" s="169" t="n"/>
+      <c r="I25" s="42">
         <f>SUM(I22:I24)</f>
         <v/>
       </c>

--- a/files/excel-mastery-1-1.xlsx
+++ b/files/excel-mastery-1-1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="1-1_体裁の対比" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1654,7 +1657,7 @@
       <c r="F8" s="44" t="n">
         <v>30</v>
       </c>
-      <c r="G8" s="191" t="n">
+      <c r="G8" s="192" t="n">
         <v>0.68</v>
       </c>
       <c r="H8" s="44" t="n">
@@ -1677,7 +1680,7 @@
       <c r="F9" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="192" t="n">
+      <c r="G9" s="193" t="n">
         <v>0.72</v>
       </c>
       <c r="H9" s="46" t="n">
@@ -1700,7 +1703,7 @@
       <c r="F10" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="193" t="n">
+      <c r="G10" s="194" t="n">
         <v>0.65</v>
       </c>
       <c r="H10" s="48" t="n">
@@ -1830,7 +1833,7 @@
           <t>52000円</t>
         </is>
       </c>
-      <c r="I22" s="194">
+      <c r="I22" s="195">
         <f>E22*F22*G22*H22/10^3</f>
         <v/>
       </c>
@@ -1882,15 +1885,15 @@
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="D25" s="167" t="inlineStr">
+      <c r="D25" s="189" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E25" s="195" t="n"/>
-      <c r="F25" s="195" t="n"/>
-      <c r="G25" s="195" t="n"/>
-      <c r="H25" s="169" t="n"/>
+      <c r="E25" s="196" t="n"/>
+      <c r="F25" s="196" t="n"/>
+      <c r="G25" s="196" t="n"/>
+      <c r="H25" s="191" t="n"/>
       <c r="I25" s="42">
         <f>SUM(I22:I24)</f>
         <v/>
